--- a/LectioShed7.8/app_data/template_souhaits_SA_20242025.xlsx
+++ b/LectioShed7.8/app_data/template_souhaits_SA_20242025.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mrani/Documents/codage/Valides/Testing/LectioShed7.7/app_data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mrani/Documents/codage/Valides/Testing/LectioShed7.8/app_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C069F7E-8AC6-3F40-A597-5847B1579F37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EB7DD28-E7E9-1044-AAB1-A4EF53864E16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="105">
   <si>
     <t>Enseignant</t>
   </si>
@@ -344,6 +344,9 @@
   </si>
   <si>
     <t>PHYSIQUE DES MATÉRIAUX</t>
+  </si>
+  <si>
+    <t>ELECTROMAGNETISME-C</t>
   </si>
 </sst>
 </file>
@@ -803,7 +806,7 @@
         <v>0</v>
       </c>
       <c r="J2" t="s">
-        <v>23</v>
+        <v>104</v>
       </c>
       <c r="L2">
         <v>2</v>
@@ -898,7 +901,7 @@
         <v>68</v>
       </c>
       <c r="B6" t="s">
-        <v>23</v>
+        <v>104</v>
       </c>
       <c r="C6">
         <v>1</v>
@@ -1263,7 +1266,7 @@
         <v>2</v>
       </c>
       <c r="F16" t="s">
-        <v>23</v>
+        <v>104</v>
       </c>
       <c r="H16">
         <v>2</v>
@@ -2063,7 +2066,7 @@
         <v>0</v>
       </c>
       <c r="F41" t="s">
-        <v>23</v>
+        <v>104</v>
       </c>
       <c r="G41">
         <v>0</v>
@@ -2133,7 +2136,7 @@
         <v>0</v>
       </c>
       <c r="F43" t="s">
-        <v>23</v>
+        <v>104</v>
       </c>
       <c r="H43">
         <v>0</v>
